--- a/data/nzd0274/nzd0274.xlsx
+++ b/data/nzd0274/nzd0274.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G351"/>
+  <dimension ref="A1:G352"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9897,7 +9897,7 @@
         <v>314.85</v>
       </c>
       <c r="C351" t="n">
-        <v>274.06</v>
+        <v>273.19</v>
       </c>
       <c r="D351" t="n">
         <v>307.31</v>
@@ -9911,6 +9911,33 @@
       <c r="G351" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:06:42+00:00</t>
+        </is>
+      </c>
+      <c r="B352" t="n">
+        <v>315.28</v>
+      </c>
+      <c r="C352" t="n">
+        <v>275.94</v>
+      </c>
+      <c r="D352" t="n">
+        <v>308.13</v>
+      </c>
+      <c r="E352" t="n">
+        <v>319.58</v>
+      </c>
+      <c r="F352" t="n">
+        <v>326.11</v>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -9925,7 +9952,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B383"/>
+  <dimension ref="A1:B384"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13758,6 +13785,16 @@
       </c>
       <c r="B383" t="n">
         <v>-0.57</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B384" t="n">
+        <v>0.32</v>
       </c>
     </row>
   </sheetData>
@@ -13926,28 +13963,28 @@
         <v>0.0885</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1433933770587509</v>
+        <v>-0.1417977227162608</v>
       </c>
       <c r="J2" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K2" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03258286871410976</v>
+        <v>0.03203588349860431</v>
       </c>
       <c r="M2" t="n">
-        <v>4.562385070085429</v>
+        <v>4.555935966314972</v>
       </c>
       <c r="N2" t="n">
-        <v>33.37530248096453</v>
+        <v>33.30494769346217</v>
       </c>
       <c r="O2" t="n">
-        <v>5.77713618334937</v>
+        <v>5.771043899803758</v>
       </c>
       <c r="P2" t="n">
-        <v>316.0481960834244</v>
+        <v>316.0316991286461</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -14004,28 +14041,28 @@
         <v>0.0526</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3834170882554856</v>
+        <v>-0.390194670388026</v>
       </c>
       <c r="J3" t="n">
+        <v>351</v>
+      </c>
+      <c r="K3" t="n">
         <v>350</v>
       </c>
-      <c r="K3" t="n">
-        <v>349</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.02154087316002518</v>
+        <v>0.02238795083962042</v>
       </c>
       <c r="M3" t="n">
-        <v>15.24034644780351</v>
+        <v>15.2371690795042</v>
       </c>
       <c r="N3" t="n">
-        <v>365.9018288979479</v>
+        <v>365.3124235974524</v>
       </c>
       <c r="O3" t="n">
-        <v>19.12856055478164</v>
+        <v>19.11314792485666</v>
       </c>
       <c r="P3" t="n">
-        <v>297.5961279469757</v>
+        <v>297.666070082131</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -14082,28 +14119,28 @@
         <v>0.193</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2444365124077875</v>
+        <v>-0.2454351480068946</v>
       </c>
       <c r="J4" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K4" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L4" t="n">
-        <v>0.08534694076013849</v>
+        <v>0.08640708154297772</v>
       </c>
       <c r="M4" t="n">
-        <v>4.290867992820663</v>
+        <v>4.283666412812215</v>
       </c>
       <c r="N4" t="n">
-        <v>35.00605407537513</v>
+        <v>34.91600869160688</v>
       </c>
       <c r="O4" t="n">
-        <v>5.916591423731669</v>
+        <v>5.908976958121166</v>
       </c>
       <c r="P4" t="n">
-        <v>316.3413386509678</v>
+        <v>316.3516632218224</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -14160,28 +14197,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2024600599060479</v>
+        <v>-0.2020994131610403</v>
       </c>
       <c r="J5" t="n">
+        <v>351</v>
+      </c>
+      <c r="K5" t="n">
         <v>350</v>
       </c>
-      <c r="K5" t="n">
-        <v>349</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.1361979488103657</v>
+        <v>0.1364293228778221</v>
       </c>
       <c r="M5" t="n">
-        <v>2.749170392282174</v>
+        <v>2.742931882342277</v>
       </c>
       <c r="N5" t="n">
-        <v>14.24170400158648</v>
+        <v>14.20228112288362</v>
       </c>
       <c r="O5" t="n">
-        <v>3.773818225827323</v>
+        <v>3.768591397708648</v>
       </c>
       <c r="P5" t="n">
-        <v>324.1792936101746</v>
+        <v>324.1755669298997</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -14238,28 +14275,28 @@
         <v>0.131</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3769050312235618</v>
+        <v>-0.3764209468080985</v>
       </c>
       <c r="J6" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K6" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L6" t="n">
-        <v>0.343645976503584</v>
+        <v>0.3443012125696282</v>
       </c>
       <c r="M6" t="n">
-        <v>2.915307992675696</v>
+        <v>2.909322997618797</v>
       </c>
       <c r="N6" t="n">
-        <v>14.83314790841899</v>
+        <v>14.79316445598226</v>
       </c>
       <c r="O6" t="n">
-        <v>3.851382596992798</v>
+        <v>3.846188302200278</v>
       </c>
       <c r="P6" t="n">
-        <v>335.011373006105</v>
+        <v>335.0063682137147</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -14297,7 +14334,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G351"/>
+  <dimension ref="A1:G352"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27255,7 +27292,7 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>-38.7993505710038,174.59053065764488</t>
+          <t>-38.79935283112769,174.59054024876963</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -27276,6 +27313,43 @@
       <c r="G351" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:06:42+00:00</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>-38.7999114055477,174.58980702961594</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>-38.799345687055165,174.590509931998</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>-38.79859413690268,174.59042426795673</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>-38.79789646024803,174.59056724965308</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>-38.79721155899281,174.5907644715042</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>

--- a/data/nzd0274/nzd0274.xlsx
+++ b/data/nzd0274/nzd0274.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G352"/>
+  <dimension ref="A1:G353"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9897,7 +9897,7 @@
         <v>314.85</v>
       </c>
       <c r="C351" t="n">
-        <v>273.19</v>
+        <v>274.06</v>
       </c>
       <c r="D351" t="n">
         <v>307.31</v>
@@ -9924,7 +9924,7 @@
         <v>315.28</v>
       </c>
       <c r="C352" t="n">
-        <v>275.94</v>
+        <v>277.15</v>
       </c>
       <c r="D352" t="n">
         <v>308.13</v>
@@ -9936,6 +9936,33 @@
         <v>326.11</v>
       </c>
       <c r="G352" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:26+00:00</t>
+        </is>
+      </c>
+      <c r="B353" t="n">
+        <v>313.85</v>
+      </c>
+      <c r="C353" t="n">
+        <v>284.6</v>
+      </c>
+      <c r="D353" t="n">
+        <v>313.02</v>
+      </c>
+      <c r="E353" t="n">
+        <v>321.39</v>
+      </c>
+      <c r="F353" t="n">
+        <v>327.33</v>
+      </c>
+      <c r="G353" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -9952,7 +9979,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B384"/>
+  <dimension ref="A1:B385"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13795,6 +13822,16 @@
       </c>
       <c r="B384" t="n">
         <v>0.32</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B385" t="n">
+        <v>-0.51</v>
       </c>
     </row>
   </sheetData>
@@ -13963,28 +14000,28 @@
         <v>0.0885</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1417977227162608</v>
+        <v>-0.1409680739676152</v>
       </c>
       <c r="J2" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K2" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03203588349860431</v>
+        <v>0.03184479864940992</v>
       </c>
       <c r="M2" t="n">
-        <v>4.555935966314972</v>
+        <v>4.546330123619732</v>
       </c>
       <c r="N2" t="n">
-        <v>33.30494769346217</v>
+        <v>33.2168897964106</v>
       </c>
       <c r="O2" t="n">
-        <v>5.771043899803758</v>
+        <v>5.763409563479816</v>
       </c>
       <c r="P2" t="n">
-        <v>316.0316991286461</v>
+        <v>316.0230488779271</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -14041,28 +14078,28 @@
         <v>0.0526</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.390194670388026</v>
+        <v>-0.3906392509439217</v>
       </c>
       <c r="J3" t="n">
+        <v>352</v>
+      </c>
+      <c r="K3" t="n">
         <v>351</v>
       </c>
-      <c r="K3" t="n">
-        <v>350</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.02238795083962042</v>
+        <v>0.02257204392679324</v>
       </c>
       <c r="M3" t="n">
-        <v>15.2371690795042</v>
+        <v>15.19623194516011</v>
       </c>
       <c r="N3" t="n">
-        <v>365.3124235974524</v>
+        <v>364.1502855531116</v>
       </c>
       <c r="O3" t="n">
-        <v>19.11314792485666</v>
+        <v>19.08272217355563</v>
       </c>
       <c r="P3" t="n">
-        <v>297.666070082131</v>
+        <v>297.670811986883</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -14119,28 +14156,28 @@
         <v>0.193</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2454351480068946</v>
+        <v>-0.2437531876492154</v>
       </c>
       <c r="J4" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K4" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L4" t="n">
-        <v>0.08640708154297772</v>
+        <v>0.08571701805275267</v>
       </c>
       <c r="M4" t="n">
-        <v>4.283666412812215</v>
+        <v>4.280626494812457</v>
       </c>
       <c r="N4" t="n">
-        <v>34.91600869160688</v>
+        <v>34.84377071134089</v>
       </c>
       <c r="O4" t="n">
-        <v>5.908976958121166</v>
+        <v>5.90286123090666</v>
       </c>
       <c r="P4" t="n">
-        <v>316.3516632218224</v>
+        <v>316.3341264283095</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -14197,28 +14234,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2020994131610403</v>
+        <v>-0.2007389501741872</v>
       </c>
       <c r="J5" t="n">
+        <v>352</v>
+      </c>
+      <c r="K5" t="n">
         <v>351</v>
       </c>
-      <c r="K5" t="n">
-        <v>350</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.1364293228778221</v>
+        <v>0.1353711039397991</v>
       </c>
       <c r="M5" t="n">
-        <v>2.742931882342277</v>
+        <v>2.741153511826789</v>
       </c>
       <c r="N5" t="n">
-        <v>14.20228112288362</v>
+        <v>14.1795136189248</v>
       </c>
       <c r="O5" t="n">
-        <v>3.768591397708648</v>
+        <v>3.765569494634881</v>
       </c>
       <c r="P5" t="n">
-        <v>324.1755669298997</v>
+        <v>324.1613889755176</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -14275,28 +14312,28 @@
         <v>0.131</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3764209468080985</v>
+        <v>-0.3752358164373093</v>
       </c>
       <c r="J6" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K6" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3443012125696282</v>
+        <v>0.343971712818918</v>
       </c>
       <c r="M6" t="n">
-        <v>2.909322997618797</v>
+        <v>2.906624662599508</v>
       </c>
       <c r="N6" t="n">
-        <v>14.79316445598226</v>
+        <v>14.7645211200733</v>
       </c>
       <c r="O6" t="n">
-        <v>3.846188302200278</v>
+        <v>3.842462897683372</v>
       </c>
       <c r="P6" t="n">
-        <v>335.0063682137147</v>
+        <v>334.9940115689796</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -14334,7 +14371,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G352"/>
+  <dimension ref="A1:G353"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27292,7 +27329,7 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>-38.79935283112769,174.59054024876963</t>
+          <t>-38.7993505710038,174.59053065764488</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -27329,7 +27366,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>-38.799345687055165,174.590509931998</t>
+          <t>-38.799342543660735,174.59049659262035</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -27348,6 +27385,43 @@
         </is>
       </c>
       <c r="G352" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:26+00:00</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>-38.79991512054737,174.58982279443342</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>-38.79932318966904,174.59041446176613</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>-38.79858143332963,174.59037035983934</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>-38.797891758115625,174.59054729612396</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>-38.79720838960991,174.59075102228957</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
         <is>
           <t>L8</t>
         </is>

--- a/data/nzd0274/nzd0274.xlsx
+++ b/data/nzd0274/nzd0274.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G353"/>
+  <dimension ref="A1:G355"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9965,6 +9965,60 @@
       <c r="G353" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:06:25+00:00</t>
+        </is>
+      </c>
+      <c r="B354" t="n">
+        <v>315.41</v>
+      </c>
+      <c r="C354" t="n">
+        <v>289.93</v>
+      </c>
+      <c r="D354" t="n">
+        <v>313.34</v>
+      </c>
+      <c r="E354" t="n">
+        <v>321.23</v>
+      </c>
+      <c r="F354" t="n">
+        <v>327.78</v>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:06:21+00:00</t>
+        </is>
+      </c>
+      <c r="B355" t="n">
+        <v>314.85</v>
+      </c>
+      <c r="C355" t="n">
+        <v>292.04</v>
+      </c>
+      <c r="D355" t="n">
+        <v>314.97</v>
+      </c>
+      <c r="E355" t="n">
+        <v>321.77</v>
+      </c>
+      <c r="F355" t="n">
+        <v>328.73</v>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -9979,7 +10033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B385"/>
+  <dimension ref="A1:B387"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13832,6 +13886,26 @@
       </c>
       <c r="B385" t="n">
         <v>-0.51</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B386" t="n">
+        <v>-0.37</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B387" t="n">
+        <v>0.58</v>
       </c>
     </row>
   </sheetData>
@@ -14000,28 +14074,28 @@
         <v>0.0885</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1409680739676152</v>
+        <v>-0.1379500915484272</v>
       </c>
       <c r="J2" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="K2" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03184479864940992</v>
+        <v>0.03083878565226794</v>
       </c>
       <c r="M2" t="n">
-        <v>4.546330123619732</v>
+        <v>4.533058380534764</v>
       </c>
       <c r="N2" t="n">
-        <v>33.2168897964106</v>
+        <v>33.07331586990084</v>
       </c>
       <c r="O2" t="n">
-        <v>5.763409563479816</v>
+        <v>5.75094043352049</v>
       </c>
       <c r="P2" t="n">
-        <v>316.0230488779271</v>
+        <v>315.9914729889987</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -14078,28 +14152,28 @@
         <v>0.0526</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3906392509439217</v>
+        <v>-0.3867900677120165</v>
       </c>
       <c r="J3" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="K3" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02257204392679324</v>
+        <v>0.02238493886944637</v>
       </c>
       <c r="M3" t="n">
-        <v>15.19623194516011</v>
+        <v>15.12768245395081</v>
       </c>
       <c r="N3" t="n">
-        <v>364.1502855531116</v>
+        <v>362.1644250580785</v>
       </c>
       <c r="O3" t="n">
-        <v>19.08272217355563</v>
+        <v>19.03061809448339</v>
       </c>
       <c r="P3" t="n">
-        <v>297.670811986883</v>
+        <v>297.6305786889001</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -14156,28 +14230,28 @@
         <v>0.193</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2437531876492154</v>
+        <v>-0.2392072893749818</v>
       </c>
       <c r="J4" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="K4" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="L4" t="n">
-        <v>0.08571701805275267</v>
+        <v>0.08346122637753772</v>
       </c>
       <c r="M4" t="n">
-        <v>4.280626494812457</v>
+        <v>4.280782954372697</v>
       </c>
       <c r="N4" t="n">
-        <v>34.84377071134089</v>
+        <v>34.74960685219021</v>
       </c>
       <c r="O4" t="n">
-        <v>5.90286123090666</v>
+        <v>5.894879714819481</v>
       </c>
       <c r="P4" t="n">
-        <v>316.3341264283095</v>
+        <v>316.2865427970162</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -14234,28 +14308,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2007389501741872</v>
+        <v>-0.1979299151389005</v>
       </c>
       <c r="J5" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="K5" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1353711039397991</v>
+        <v>0.1331120830463419</v>
       </c>
       <c r="M5" t="n">
-        <v>2.741153511826789</v>
+        <v>2.738205868529776</v>
       </c>
       <c r="N5" t="n">
-        <v>14.1795136189248</v>
+        <v>14.13751425783035</v>
       </c>
       <c r="O5" t="n">
-        <v>3.765569494634881</v>
+        <v>3.75998859809845</v>
       </c>
       <c r="P5" t="n">
-        <v>324.1613889755176</v>
+        <v>324.1320033409199</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -14312,28 +14386,28 @@
         <v>0.131</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3752358164373093</v>
+        <v>-0.3718831115420359</v>
       </c>
       <c r="J6" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="K6" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="L6" t="n">
-        <v>0.343971712818918</v>
+        <v>0.3416691130288332</v>
       </c>
       <c r="M6" t="n">
-        <v>2.906624662599508</v>
+        <v>2.905885777740254</v>
       </c>
       <c r="N6" t="n">
-        <v>14.7645211200733</v>
+        <v>14.73623093344755</v>
       </c>
       <c r="O6" t="n">
-        <v>3.842462897683372</v>
+        <v>3.838779875617714</v>
       </c>
       <c r="P6" t="n">
-        <v>334.9940115689796</v>
+        <v>334.9589196779597</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -14371,7 +14445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G353"/>
+  <dimension ref="A1:G355"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27427,6 +27501,80 @@
         </is>
       </c>
     </row>
+    <row r="354">
+      <c r="A354" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:06:25+00:00</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>-38.79991106782033,174.5898055964508</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>-38.7993093430859,174.5903557024026</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>-38.798580602011086,174.59036683211042</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>-38.79789217377388,174.59054905997172</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>-38.79720722057482,174.59074606151395</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:06:21+00:00</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>-38.79991252264572,174.58981177008536</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>-38.799303861597224,174.59033244119718</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>-38.79857636748056,174.59034886274245</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>-38.797890770927154,174.59054310698556</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>-38.79720475261119,174.590735588766</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0274/nzd0274.xlsx
+++ b/data/nzd0274/nzd0274.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G355"/>
+  <dimension ref="A1:G359"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10017,6 +10017,114 @@
         <v>328.73</v>
       </c>
       <c r="G355" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:06:04+00:00</t>
+        </is>
+      </c>
+      <c r="B356" t="n">
+        <v>315.78</v>
+      </c>
+      <c r="C356" t="n">
+        <v>292.04</v>
+      </c>
+      <c r="D356" t="n">
+        <v>313.52</v>
+      </c>
+      <c r="E356" t="n">
+        <v>322.07</v>
+      </c>
+      <c r="F356" t="n">
+        <v>327.9</v>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:06:14+00:00</t>
+        </is>
+      </c>
+      <c r="B357" t="n">
+        <v>318.16</v>
+      </c>
+      <c r="C357" t="n">
+        <v>295.62</v>
+      </c>
+      <c r="D357" t="n">
+        <v>314.78</v>
+      </c>
+      <c r="E357" t="n">
+        <v>323.41</v>
+      </c>
+      <c r="F357" t="n">
+        <v>330.05</v>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:05:59+00:00</t>
+        </is>
+      </c>
+      <c r="B358" t="n">
+        <v>314.33</v>
+      </c>
+      <c r="C358" t="n">
+        <v>295.62</v>
+      </c>
+      <c r="D358" t="n">
+        <v>313.79</v>
+      </c>
+      <c r="E358" t="n">
+        <v>322.87</v>
+      </c>
+      <c r="F358" t="n">
+        <v>329.23</v>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:11+00:00</t>
+        </is>
+      </c>
+      <c r="B359" t="n">
+        <v>314.05</v>
+      </c>
+      <c r="C359" t="n">
+        <v>314.51</v>
+      </c>
+      <c r="D359" t="n">
+        <v>314.53</v>
+      </c>
+      <c r="E359" t="n">
+        <v>324.12</v>
+      </c>
+      <c r="F359" t="n">
+        <v>332.57</v>
+      </c>
+      <c r="G359" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -10033,7 +10141,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B387"/>
+  <dimension ref="A1:B391"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13906,6 +14014,46 @@
       </c>
       <c r="B387" t="n">
         <v>0.58</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B388" t="n">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B389" t="n">
+        <v>-0.03</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B390" t="n">
+        <v>1.09</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B391" t="n">
+        <v>-0.82</v>
       </c>
     </row>
   </sheetData>
@@ -14074,28 +14222,28 @@
         <v>0.0885</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1379500915484272</v>
+        <v>-0.1311891338469023</v>
       </c>
       <c r="J2" t="n">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="K2" t="n">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03083878565226794</v>
+        <v>0.02847258770948269</v>
       </c>
       <c r="M2" t="n">
-        <v>4.533058380534764</v>
+        <v>4.510097980385966</v>
       </c>
       <c r="N2" t="n">
-        <v>33.07331586990084</v>
+        <v>32.84555115137289</v>
       </c>
       <c r="O2" t="n">
-        <v>5.75094043352049</v>
+        <v>5.731103833588508</v>
       </c>
       <c r="P2" t="n">
-        <v>315.9914729889987</v>
+        <v>315.9204587324877</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -14152,28 +14300,28 @@
         <v>0.0526</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3867900677120165</v>
+        <v>-0.3615256006735932</v>
       </c>
       <c r="J3" t="n">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="K3" t="n">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02238493886944637</v>
+        <v>0.01991842467849447</v>
       </c>
       <c r="M3" t="n">
-        <v>15.12768245395081</v>
+        <v>15.07102047832788</v>
       </c>
       <c r="N3" t="n">
-        <v>362.1644250580785</v>
+        <v>360.5399392136789</v>
       </c>
       <c r="O3" t="n">
-        <v>19.03061809448339</v>
+        <v>18.98788927747576</v>
       </c>
       <c r="P3" t="n">
-        <v>297.6305786889001</v>
+        <v>297.3653369121984</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -14230,28 +14378,28 @@
         <v>0.193</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2392072893749818</v>
+        <v>-0.2304545209507236</v>
       </c>
       <c r="J4" t="n">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="K4" t="n">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="L4" t="n">
-        <v>0.08346122637753772</v>
+        <v>0.07916447333760201</v>
       </c>
       <c r="M4" t="n">
-        <v>4.280782954372697</v>
+        <v>4.278941312430523</v>
       </c>
       <c r="N4" t="n">
-        <v>34.74960685219021</v>
+        <v>34.55213667940691</v>
       </c>
       <c r="O4" t="n">
-        <v>5.894879714819481</v>
+        <v>5.878106555635659</v>
       </c>
       <c r="P4" t="n">
-        <v>316.2865427970162</v>
+        <v>316.1945673533329</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -14308,28 +14456,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1979299151389005</v>
+        <v>-0.189118242587552</v>
       </c>
       <c r="J5" t="n">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="K5" t="n">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1331120830463419</v>
+        <v>0.1238705449610128</v>
       </c>
       <c r="M5" t="n">
-        <v>2.738205868529776</v>
+        <v>2.747146775377449</v>
       </c>
       <c r="N5" t="n">
-        <v>14.13751425783035</v>
+        <v>14.17629388516465</v>
       </c>
       <c r="O5" t="n">
-        <v>3.75998859809845</v>
+        <v>3.765141947545225</v>
       </c>
       <c r="P5" t="n">
-        <v>324.1320033409199</v>
+        <v>324.0394395005162</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -14386,28 +14534,28 @@
         <v>0.131</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3718831115420359</v>
+        <v>-0.3618590337893243</v>
       </c>
       <c r="J6" t="n">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="K6" t="n">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3416691130288332</v>
+        <v>0.3302849590174721</v>
       </c>
       <c r="M6" t="n">
-        <v>2.905885777740254</v>
+        <v>2.920693992330515</v>
       </c>
       <c r="N6" t="n">
-        <v>14.73623093344755</v>
+        <v>14.8502169835642</v>
       </c>
       <c r="O6" t="n">
-        <v>3.838779875617714</v>
+        <v>3.853597927075968</v>
       </c>
       <c r="P6" t="n">
-        <v>334.9589196779597</v>
+        <v>334.853553479041</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -14445,7 +14593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G355"/>
+  <dimension ref="A1:G359"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27575,6 +27723,154 @@
         </is>
       </c>
     </row>
+    <row r="356">
+      <c r="A356" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:06:04+00:00</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>-38.79991010659624,174.58980151744237</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>-38.799303861597224,174.59033244119718</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>-38.79858013439436,174.59036484776294</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>-38.797889991567736,174.5905397997711</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>-38.79720690883211,174.59074473864052</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:06:14+00:00</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>-38.79990392358373,174.58977527949878</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>-38.79929456124071,174.59029297432568</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>-38.79857686107628,174.59035095733125</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>-38.79788651042784,174.59052502754744</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>-38.79720132343906,174.59072103715943</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:05:59+00:00</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>-38.79991387355472,174.58981750274626</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>-38.79929456124071,174.59029297432568</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>-38.79857943296919,174.59036187124178</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>-38.79788791327548,174.59053098053295</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>-38.79720345368257,174.59073007679365</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:11+00:00</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>-38.79991460096713,174.58982058956374</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>-38.799245487347186,174.59008472610805</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>-38.798577510544284,174.59035371336918</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>-38.7978846659425,174.59051720047427</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>-38.79719477683262,174.59069325682333</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0274/nzd0274.xlsx
+++ b/data/nzd0274/nzd0274.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G359"/>
+  <dimension ref="A1:G362"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10113,13 +10113,13 @@
         <v>314.05</v>
       </c>
       <c r="C359" t="n">
-        <v>314.51</v>
+        <v>299.33</v>
       </c>
       <c r="D359" t="n">
         <v>314.53</v>
       </c>
       <c r="E359" t="n">
-        <v>324.12</v>
+        <v>328.53</v>
       </c>
       <c r="F359" t="n">
         <v>332.57</v>
@@ -10127,6 +10127,87 @@
       <c r="G359" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:53+00:00</t>
+        </is>
+      </c>
+      <c r="B360" t="n">
+        <v>316.31</v>
+      </c>
+      <c r="C360" t="n">
+        <v>299.33</v>
+      </c>
+      <c r="D360" t="n">
+        <v>314.56</v>
+      </c>
+      <c r="E360" t="n">
+        <v>328.22</v>
+      </c>
+      <c r="F360" t="n">
+        <v>332.28</v>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:05:59+00:00</t>
+        </is>
+      </c>
+      <c r="B361" t="n">
+        <v>313.23</v>
+      </c>
+      <c r="C361" t="n">
+        <v>294.18</v>
+      </c>
+      <c r="D361" t="n">
+        <v>311.85</v>
+      </c>
+      <c r="E361" t="n">
+        <v>326.08</v>
+      </c>
+      <c r="F361" t="n">
+        <v>329.84</v>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:32+00:00</t>
+        </is>
+      </c>
+      <c r="B362" t="n">
+        <v>317.48</v>
+      </c>
+      <c r="C362" t="n">
+        <v>287.53</v>
+      </c>
+      <c r="D362" t="n">
+        <v>312.36</v>
+      </c>
+      <c r="E362" t="n">
+        <v>327.2</v>
+      </c>
+      <c r="F362" t="n">
+        <v>330.44</v>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -10141,7 +10222,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B391"/>
+  <dimension ref="A1:B394"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14054,6 +14135,36 @@
       </c>
       <c r="B391" t="n">
         <v>-0.82</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B392" t="n">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B393" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B394" t="n">
+        <v>1.67</v>
       </c>
     </row>
   </sheetData>
@@ -14222,28 +14333,28 @@
         <v>0.0885</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1311891338469023</v>
+        <v>-0.1262107310972436</v>
       </c>
       <c r="J2" t="n">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="K2" t="n">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02847258770948269</v>
+        <v>0.02674799671754258</v>
       </c>
       <c r="M2" t="n">
-        <v>4.510097980385966</v>
+        <v>4.493450281239403</v>
       </c>
       <c r="N2" t="n">
-        <v>32.84555115137289</v>
+        <v>32.68322483326457</v>
       </c>
       <c r="O2" t="n">
-        <v>5.731103833588508</v>
+        <v>5.716924420810947</v>
       </c>
       <c r="P2" t="n">
-        <v>315.9204587324877</v>
+        <v>315.8679496688352</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -14300,28 +14411,28 @@
         <v>0.0526</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3615256006735932</v>
+        <v>-0.3602530703413033</v>
       </c>
       <c r="J3" t="n">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="K3" t="n">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01991842467849447</v>
+        <v>0.02016693749448917</v>
       </c>
       <c r="M3" t="n">
-        <v>15.07102047832788</v>
+        <v>14.95256078625903</v>
       </c>
       <c r="N3" t="n">
-        <v>360.5399392136789</v>
+        <v>356.4064338789846</v>
       </c>
       <c r="O3" t="n">
-        <v>18.98788927747576</v>
+        <v>18.87872966804135</v>
       </c>
       <c r="P3" t="n">
-        <v>297.3653369121984</v>
+        <v>297.3518303660471</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -14378,28 +14489,28 @@
         <v>0.193</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2304545209507236</v>
+        <v>-0.2261005142044889</v>
       </c>
       <c r="J4" t="n">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="K4" t="n">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="L4" t="n">
-        <v>0.07916447333760201</v>
+        <v>0.07744349218248225</v>
       </c>
       <c r="M4" t="n">
-        <v>4.278941312430523</v>
+        <v>4.266378427062477</v>
       </c>
       <c r="N4" t="n">
-        <v>34.55213667940691</v>
+        <v>34.34072342651064</v>
       </c>
       <c r="O4" t="n">
-        <v>5.878106555635659</v>
+        <v>5.860095854720351</v>
       </c>
       <c r="P4" t="n">
-        <v>316.1945673533329</v>
+        <v>316.1486626714591</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -14456,28 +14567,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.189118242587552</v>
+        <v>-0.1742945904856646</v>
       </c>
       <c r="J5" t="n">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="K5" t="n">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1238705449610128</v>
+        <v>0.1040819160187173</v>
       </c>
       <c r="M5" t="n">
-        <v>2.747146775377449</v>
+        <v>2.79471817734492</v>
       </c>
       <c r="N5" t="n">
-        <v>14.17629388516465</v>
+        <v>14.77346298125023</v>
       </c>
       <c r="O5" t="n">
-        <v>3.765141947545225</v>
+        <v>3.843626280122747</v>
       </c>
       <c r="P5" t="n">
-        <v>324.0394395005162</v>
+        <v>323.8832327435686</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -14534,28 +14645,28 @@
         <v>0.131</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3618590337893243</v>
+        <v>-0.3532648204409024</v>
       </c>
       <c r="J6" t="n">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="K6" t="n">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3302849590174721</v>
+        <v>0.3195348935165998</v>
       </c>
       <c r="M6" t="n">
-        <v>2.920693992330515</v>
+        <v>2.937104130013517</v>
       </c>
       <c r="N6" t="n">
-        <v>14.8502169835642</v>
+        <v>14.98603154868985</v>
       </c>
       <c r="O6" t="n">
-        <v>3.853597927075968</v>
+        <v>3.871179606875642</v>
       </c>
       <c r="P6" t="n">
-        <v>334.853553479041</v>
+        <v>334.7629294366158</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -14593,7 +14704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G359"/>
+  <dimension ref="A1:G362"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27847,7 +27958,7 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>-38.799245487347186,174.59008472610805</t>
+          <t>-38.79928492314744,174.59025207431</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -27857,7 +27968,7 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>-38.7978846659425,174.59051720047427</t>
+          <t>-38.79787320933844,174.59046858443693</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
@@ -27868,6 +27979,117 @@
       <c r="G359" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:53+00:00</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>-38.799908729707425,174.58979567453858</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>-38.79928492314744,174.59025207431</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>-38.798577432608134,174.59035338264462</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>-38.79787401467863,174.5904720018903</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>-38.79719553021228,174.59069645376653</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:05:59+00:00</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>-38.79991673124585,174.5898296295296</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>-38.79929830216787,174.59030884926722</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>-38.79858447283714,174.5903832580989</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>-38.79787957412102,174.5904955933447</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>-38.797201868989305,174.59072335218764</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:32+00:00</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>-38.79990569015934,174.58978277605365</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>-38.799315577948825,174.59038216064988</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>-38.79858314792379,174.5903776357805</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>-38.79787666450691,174.59048324641486</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>-38.797200310274214,174.59071673782137</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>

--- a/data/nzd0274/nzd0274.xlsx
+++ b/data/nzd0274/nzd0274.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G362"/>
+  <dimension ref="A1:G363"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10208,6 +10208,33 @@
       <c r="G362" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:42+00:00</t>
+        </is>
+      </c>
+      <c r="B363" t="n">
+        <v>317.24</v>
+      </c>
+      <c r="C363" t="n">
+        <v>281.94</v>
+      </c>
+      <c r="D363" t="n">
+        <v>310.34</v>
+      </c>
+      <c r="E363" t="n">
+        <v>326.59</v>
+      </c>
+      <c r="F363" t="n">
+        <v>330.68</v>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -10222,7 +10249,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B394"/>
+  <dimension ref="A1:B395"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14165,6 +14192,16 @@
       </c>
       <c r="B394" t="n">
         <v>1.67</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B395" t="n">
+        <v>-0.77</v>
       </c>
     </row>
   </sheetData>
@@ -14333,28 +14370,28 @@
         <v>0.0885</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1262107310972436</v>
+        <v>-0.1237775897586728</v>
       </c>
       <c r="J2" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="K2" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02674799671754258</v>
+        <v>0.02584348413265602</v>
       </c>
       <c r="M2" t="n">
-        <v>4.493450281239403</v>
+        <v>4.491143714905702</v>
       </c>
       <c r="N2" t="n">
-        <v>32.68322483326457</v>
+        <v>32.65393498058566</v>
       </c>
       <c r="O2" t="n">
-        <v>5.716924420810947</v>
+        <v>5.714362167432657</v>
       </c>
       <c r="P2" t="n">
-        <v>315.8679496688352</v>
+        <v>315.8421815535619</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -14411,28 +14448,28 @@
         <v>0.0526</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3602530703413033</v>
+        <v>-0.3632781064567757</v>
       </c>
       <c r="J3" t="n">
+        <v>362</v>
+      </c>
+      <c r="K3" t="n">
         <v>361</v>
       </c>
-      <c r="K3" t="n">
-        <v>360</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.02016693749448917</v>
+        <v>0.02060511594215975</v>
       </c>
       <c r="M3" t="n">
-        <v>14.95256078625903</v>
+        <v>14.92991189816939</v>
       </c>
       <c r="N3" t="n">
-        <v>356.4064338789846</v>
+        <v>355.513475931611</v>
       </c>
       <c r="O3" t="n">
-        <v>18.87872966804135</v>
+        <v>18.85506499409671</v>
       </c>
       <c r="P3" t="n">
-        <v>297.3518303660471</v>
+        <v>297.3838167902361</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -14489,28 +14526,28 @@
         <v>0.193</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2261005142044889</v>
+        <v>-0.2260052929717396</v>
       </c>
       <c r="J4" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="K4" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L4" t="n">
-        <v>0.07744349218248225</v>
+        <v>0.07777477537307476</v>
       </c>
       <c r="M4" t="n">
-        <v>4.266378427062477</v>
+        <v>4.255089772270236</v>
       </c>
       <c r="N4" t="n">
-        <v>34.34072342651064</v>
+        <v>34.24595296736702</v>
       </c>
       <c r="O4" t="n">
-        <v>5.860095854720351</v>
+        <v>5.852004183813185</v>
       </c>
       <c r="P4" t="n">
-        <v>316.1486626714591</v>
+        <v>316.1476542336577</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -14567,28 +14604,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1742945904856646</v>
+        <v>-0.1705166023333529</v>
       </c>
       <c r="J5" t="n">
+        <v>362</v>
+      </c>
+      <c r="K5" t="n">
         <v>361</v>
       </c>
-      <c r="K5" t="n">
-        <v>360</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.1040819160187173</v>
+        <v>0.09966092327593812</v>
       </c>
       <c r="M5" t="n">
-        <v>2.79471817734492</v>
+        <v>2.805544755981542</v>
       </c>
       <c r="N5" t="n">
-        <v>14.77346298125023</v>
+        <v>14.88007060996527</v>
       </c>
       <c r="O5" t="n">
-        <v>3.843626280122747</v>
+        <v>3.857469456776718</v>
       </c>
       <c r="P5" t="n">
-        <v>323.8832327435686</v>
+        <v>323.8432383150526</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -14645,28 +14682,28 @@
         <v>0.131</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3532648204409024</v>
+        <v>-0.3505437564706959</v>
       </c>
       <c r="J6" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="K6" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3195348935165998</v>
+        <v>0.3162642335725389</v>
       </c>
       <c r="M6" t="n">
-        <v>2.937104130013517</v>
+        <v>2.941984262243418</v>
       </c>
       <c r="N6" t="n">
-        <v>14.98603154868985</v>
+        <v>15.02091867877162</v>
       </c>
       <c r="O6" t="n">
-        <v>3.871179606875642</v>
+        <v>3.875682995134099</v>
       </c>
       <c r="P6" t="n">
-        <v>334.7629294366158</v>
+        <v>334.7341120847674</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -14704,7 +14741,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G362"/>
+  <dimension ref="A1:G363"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28093,6 +28130,43 @@
         </is>
       </c>
     </row>
+    <row r="363">
+      <c r="A363" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:42+00:00</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>-38.79990631365651,174.58978542189664</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>-38.79933009996006,174.59044378633467</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>-38.7985883956182,174.59039990457217</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>-38.79787824920761,174.5904899710819</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>-38.797199686788076,174.59071409207496</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
